--- a/TEST CASES.xlsx
+++ b/TEST CASES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\PARTH CAREER\GIT TASK\09 MARCH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB2FCE6-A1C8-4434-93D0-5650B9AF7A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48BE2DA8-ABFD-494E-9A47-1CD871947022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,77 +25,29 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="138">
   <si>
     <t>TC_ID</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Steps</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
     <t>TC_01</t>
   </si>
   <si>
-    <t>Verify application launch</t>
-  </si>
-  <si>
-    <t>Open the ADUKUNDA app</t>
-  </si>
-  <si>
-    <t>App should open successfully</t>
-  </si>
-  <si>
     <t>TC_02</t>
   </si>
   <si>
-    <t>Verify login with valid credentials</t>
-  </si>
-  <si>
-    <t>Enter valid username and password</t>
-  </si>
-  <si>
     <t>User should login successfully</t>
   </si>
   <si>
     <t>TC_03</t>
   </si>
   <si>
-    <t>Verify login with invalid credentials</t>
-  </si>
-  <si>
-    <t>Enter incorrect username/password</t>
-  </si>
-  <si>
-    <t>Error message should display</t>
-  </si>
-  <si>
     <t>TC_04</t>
   </si>
   <si>
-    <t>Verify OTP functionality</t>
-  </si>
-  <si>
-    <t>Enter mobile number and request OTP</t>
-  </si>
-  <si>
-    <t>OTP should be received</t>
-  </si>
-  <si>
     <t>TC_05</t>
   </si>
   <si>
-    <t>Verify invalid OTP</t>
-  </si>
-  <si>
-    <t>Enter wrong OTP</t>
-  </si>
-  <si>
     <t>Error message should appear</t>
   </si>
   <si>
@@ -105,57 +57,24 @@
     <t>Verify logout functionality</t>
   </si>
   <si>
-    <t>Click logout button</t>
-  </si>
-  <si>
-    <t>User should be logged out</t>
-  </si>
-  <si>
     <t>TC_07</t>
   </si>
   <si>
-    <t>Verify navigation menu</t>
-  </si>
-  <si>
-    <t>Tap menu icon</t>
-  </si>
-  <si>
-    <t>Menu options should display</t>
-  </si>
-  <si>
     <t>TC_08</t>
   </si>
   <si>
     <t>Verify profile page access</t>
   </si>
   <si>
-    <t>Click profile option</t>
-  </si>
-  <si>
     <t>Profile page should open</t>
   </si>
   <si>
     <t>TC_09</t>
   </si>
   <si>
-    <t>Verify profile edit option</t>
-  </si>
-  <si>
-    <t>Edit profile details</t>
-  </si>
-  <si>
-    <t>Changes should be saved</t>
-  </si>
-  <si>
     <t>TC_10</t>
   </si>
   <si>
-    <t>Verify search functionality</t>
-  </si>
-  <si>
-    <t>Enter keyword in search bar</t>
-  </si>
-  <si>
     <t>Relevant results should display</t>
   </si>
   <si>
@@ -165,115 +84,361 @@
     <t>Verify notification feature</t>
   </si>
   <si>
-    <t>Trigger notification</t>
-  </si>
-  <si>
     <t>Notification should appear</t>
   </si>
   <si>
     <t>TC_12</t>
   </si>
   <si>
-    <t>Verify internet connectivity handling</t>
-  </si>
-  <si>
-    <t>Turn off internet and use app</t>
-  </si>
-  <si>
     <t>TC_13</t>
   </si>
   <si>
-    <t>Verify UI responsiveness</t>
-  </si>
-  <si>
-    <t>Rotate screen or change layout</t>
-  </si>
-  <si>
-    <t>UI should adjust correctly</t>
-  </si>
-  <si>
     <t>TC_14</t>
   </si>
   <si>
-    <t>Verify settings page</t>
-  </si>
-  <si>
-    <t>Click settings option</t>
-  </si>
-  <si>
     <t>Settings page should open</t>
   </si>
   <si>
     <t>TC_15</t>
   </si>
   <si>
-    <t>Verify help/support section</t>
-  </si>
-  <si>
-    <t>Click help option</t>
-  </si>
-  <si>
-    <t>Help information should appear</t>
-  </si>
-  <si>
     <t>TC_16</t>
   </si>
   <si>
-    <t>Verify data loading speed</t>
-  </si>
-  <si>
-    <t>Open dashboard</t>
-  </si>
-  <si>
-    <t>Data should load quickly</t>
-  </si>
-  <si>
     <t>TC_17</t>
   </si>
   <si>
-    <t>Verify button functionality</t>
-  </si>
-  <si>
-    <t>Click main action button</t>
-  </si>
-  <si>
-    <t>Correct action should occur</t>
-  </si>
-  <si>
     <t>TC_18</t>
   </si>
   <si>
     <t>Verify session timeout</t>
   </si>
   <si>
-    <t>Stay inactive for long time</t>
-  </si>
-  <si>
-    <t>User should be logged out automatically</t>
-  </si>
-  <si>
     <t>TC_19</t>
   </si>
   <si>
-    <t>Verify error handling</t>
-  </si>
-  <si>
-    <t>Perform invalid action</t>
-  </si>
-  <si>
-    <t>Proper error message should show</t>
-  </si>
-  <si>
     <t>TC_20</t>
   </si>
   <si>
-    <t>Verify application close</t>
-  </si>
-  <si>
-    <t>Close app and reopen</t>
-  </si>
-  <si>
     <t>App should restart normally</t>
+  </si>
+  <si>
+    <t>TESTING TYPE</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
+    <t>TEST DATA / INPUT</t>
+  </si>
+  <si>
+    <t>STEPS</t>
+  </si>
+  <si>
+    <t>EXPECTED RESULT</t>
+  </si>
+  <si>
+    <t>ACTUAL RESULT</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>COMMENT</t>
+  </si>
+  <si>
+    <t>Functional Testing</t>
+  </si>
+  <si>
+    <t>Verify login using valid mobile number</t>
+  </si>
+  <si>
+    <t>Mobile No: 9876543210</t>
+  </si>
+  <si>
+    <t>1. Open application 2. Enter mobile number 3. Click login 4. Enter OTP</t>
+  </si>
+  <si>
+    <t>User logged in successfully</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Login working correctly</t>
+  </si>
+  <si>
+    <t>Verify login with invalid OTP</t>
+  </si>
+  <si>
+    <t>OTP: 123456</t>
+  </si>
+  <si>
+    <t>1. Open app 2. Enter mobile number 3. Enter invalid OTP</t>
+  </si>
+  <si>
+    <t>Error message displayed</t>
+  </si>
+  <si>
+    <t>Validation working</t>
+  </si>
+  <si>
+    <t>UI Testing</t>
+  </si>
+  <si>
+    <t>Verify login button visibility</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>1. Open login page 2. Observe login button</t>
+  </si>
+  <si>
+    <t>Login button should be visible</t>
+  </si>
+  <si>
+    <t>Button visible</t>
+  </si>
+  <si>
+    <t>UI correct</t>
+  </si>
+  <si>
+    <t>1. Login to app 2. Click logout</t>
+  </si>
+  <si>
+    <t>User should logout successfully</t>
+  </si>
+  <si>
+    <t>User logged out</t>
+  </si>
+  <si>
+    <t>Logout working</t>
+  </si>
+  <si>
+    <t>Performance Testing</t>
+  </si>
+  <si>
+    <t>Verify app launch time</t>
+  </si>
+  <si>
+    <t>1. Tap app icon</t>
+  </si>
+  <si>
+    <t>App should open within 3 seconds</t>
+  </si>
+  <si>
+    <t>App opened in 2 seconds</t>
+  </si>
+  <si>
+    <t>Good performance</t>
+  </si>
+  <si>
+    <t>Security Testing</t>
+  </si>
+  <si>
+    <t>Verify OTP security</t>
+  </si>
+  <si>
+    <t>OTP</t>
+  </si>
+  <si>
+    <t>1. Request OTP 2. Enter OTP</t>
+  </si>
+  <si>
+    <t>System should validate OTP</t>
+  </si>
+  <si>
+    <t>OTP validated</t>
+  </si>
+  <si>
+    <t>Security working</t>
+  </si>
+  <si>
+    <t>Compatibility Testing</t>
+  </si>
+  <si>
+    <t>Verify app on Android device</t>
+  </si>
+  <si>
+    <t>Android 13</t>
+  </si>
+  <si>
+    <t>1. Install app 2. Launch app</t>
+  </si>
+  <si>
+    <t>App should run smoothly</t>
+  </si>
+  <si>
+    <t>App runs smoothly</t>
+  </si>
+  <si>
+    <t>No compatibility issue</t>
+  </si>
+  <si>
+    <t>Negative Testing</t>
+  </si>
+  <si>
+    <t>Verify login with empty mobile number</t>
+  </si>
+  <si>
+    <t>Blank</t>
+  </si>
+  <si>
+    <t>1. Open login page 2. Leave field empty 3. Click login</t>
+  </si>
+  <si>
+    <t>Error displayed</t>
+  </si>
+  <si>
+    <t>Input validation correct</t>
+  </si>
+  <si>
+    <t>1. Login 2. Click profile option</t>
+  </si>
+  <si>
+    <t>Profile page opened</t>
+  </si>
+  <si>
+    <t>Navigation correct</t>
+  </si>
+  <si>
+    <t>Verify profile edit feature</t>
+  </si>
+  <si>
+    <t>Name: Parth</t>
+  </si>
+  <si>
+    <t>1. Open profile 2. Edit name 3. Save</t>
+  </si>
+  <si>
+    <t>Profile should update</t>
+  </si>
+  <si>
+    <t>Profile updated</t>
+  </si>
+  <si>
+    <t>Data saved correctly</t>
+  </si>
+  <si>
+    <t>Verify menu icon display</t>
+  </si>
+  <si>
+    <t>1. Open home page</t>
+  </si>
+  <si>
+    <t>Menu icon should be visible</t>
+  </si>
+  <si>
+    <t>Icon visible</t>
+  </si>
+  <si>
+    <t>Verify search feature</t>
+  </si>
+  <si>
+    <t>Keyword: Test</t>
+  </si>
+  <si>
+    <t>1. Click search bar 2. Enter keyword</t>
+  </si>
+  <si>
+    <t>Results displayed</t>
+  </si>
+  <si>
+    <t>Search working</t>
+  </si>
+  <si>
+    <t>1. Trigger notification</t>
+  </si>
+  <si>
+    <t>Notification received</t>
+  </si>
+  <si>
+    <t>Notification working</t>
+  </si>
+  <si>
+    <t>Verify page loading speed</t>
+  </si>
+  <si>
+    <t>1. Open dashboard</t>
+  </si>
+  <si>
+    <t>Page should load quickly</t>
+  </si>
+  <si>
+    <t>Loaded in 2 sec</t>
+  </si>
+  <si>
+    <t>Acceptable speed</t>
+  </si>
+  <si>
+    <t>Verify invalid input handling</t>
+  </si>
+  <si>
+    <t>Special characters</t>
+  </si>
+  <si>
+    <t>1. Enter invalid data</t>
+  </si>
+  <si>
+    <t>Verify help section</t>
+  </si>
+  <si>
+    <t>1. Open help option</t>
+  </si>
+  <si>
+    <t>Help page should open</t>
+  </si>
+  <si>
+    <t>Help page opened</t>
+  </si>
+  <si>
+    <t>Feature working</t>
+  </si>
+  <si>
+    <t>Verify button alignment</t>
+  </si>
+  <si>
+    <t>Buttons should be aligned properly</t>
+  </si>
+  <si>
+    <t>Buttons aligned</t>
+  </si>
+  <si>
+    <t>UI proper</t>
+  </si>
+  <si>
+    <t>1. Stay inactive for some time</t>
+  </si>
+  <si>
+    <t>Session should expire</t>
+  </si>
+  <si>
+    <t>Session expired</t>
+  </si>
+  <si>
+    <t>Security good</t>
+  </si>
+  <si>
+    <t>Verify settings option</t>
+  </si>
+  <si>
+    <t>1. Open settings</t>
+  </si>
+  <si>
+    <t>Settings page opened</t>
+  </si>
+  <si>
+    <t>Verify app close and reopen</t>
+  </si>
+  <si>
+    <t>1. Close app 2. Reopen app</t>
+  </si>
+  <si>
+    <t>App restarted</t>
+  </si>
+  <si>
+    <t>App stable</t>
   </si>
 </sst>
 </file>
@@ -335,13 +500,13 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -623,308 +788,626 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultRowHeight="50.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.5703125" style="2" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" style="2" customWidth="1"/>
     <col min="4" max="4" width="26.7109375" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="2"/>
+    <col min="5" max="5" width="29.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="B11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="C19" s="3" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>82</v>
+        <v>54</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
